--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="84">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>1.12- Document de référence</t>
+    <t>Document de référence</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,97 +260,7 @@
     <t>Type de référence.</t>
   </si>
   <si>
-    <t>DocumentReference.parentDocument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Document de référence.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>DocumentReference.parentDocument.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.parentDocument.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>DocumentReference.parentDocument.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>DocumentReference.parentDocument.identifiantUniqueDocument</t>
+    <t>DocumentReference.identifiantUniqueDocument</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -659,24 +569,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ8"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="61.92578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="61.92578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.79296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.79296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="21.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="17.66015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="17.24609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -690,10 +600,10 @@
     <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="61.92578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.79296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1106,412 +1016,6 @@
         <v>72</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L5" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF5" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K6" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="P6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AG6" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH6" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI6" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="P7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF7" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="S8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-DocumentReference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
